--- a/out/Village_map_of_Tiruvallur_Gummidipoondi_Vanrasikuppam_13.402641_79.951224.xlsx
+++ b/out/Village_map_of_Tiruvallur_Gummidipoondi_Vanrasikuppam_13.402641_79.951224.xlsx
@@ -830,11 +830,6 @@
           <t>129</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>1A, 1B, 1C, 1D, 2A1, 2A2, 2B, 2C, 2D1, 2D2, 3A, 3B, 3C</t>
-        </is>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -842,11 +837,6 @@
           <t>13</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>1, 2</t>
-        </is>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -854,11 +844,6 @@
           <t>130</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>1, 2</t>
-        </is>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -866,11 +851,6 @@
           <t>131</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>1, 2</t>
-        </is>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -878,11 +858,6 @@
           <t>132</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -890,11 +865,6 @@
           <t>133</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>10, 11, 12, 1A, 1B, 2, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -902,11 +872,6 @@
           <t>134</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>1, 10, 11A, 11B, 12A, 12B, 13, 14, 15, 16, 17, 18A, 18B, 19, 20, 21, 2A, 2B, 3A, 3B, 4A, 4B, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -914,11 +879,6 @@
           <t>135</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>1, 2</t>
-        </is>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -926,11 +886,6 @@
           <t>136</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>10, 11, 1A, 1B, 2, 3, 4, 5A, 5B, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -938,11 +893,6 @@
           <t>137</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 2, 3, 4, 5, 6, 7, 8, 9A, 9B</t>
-        </is>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -950,11 +900,6 @@
           <t>138</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -962,11 +907,6 @@
           <t>139</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -974,11 +914,6 @@
           <t>14</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>1, 2A, 2B, 2C, 3A, 3B, 3C, 3D, 4A, 4B, 4C, 4D, 4E, 4F</t>
-        </is>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -986,11 +921,6 @@
           <t>140</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>1A, 1B, 2, 3</t>
-        </is>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -998,11 +928,6 @@
           <t>141</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>1, 2</t>
-        </is>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1010,11 +935,6 @@
           <t>142</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4</t>
-        </is>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1022,11 +942,6 @@
           <t>143</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13A, 13B, 2, 3, 4, 5, 6, 7, 8, 9A, 9B</t>
-        </is>
-      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1034,11 +949,6 @@
           <t>144</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>1A, 1B, 1C, 1D, 2A1A, 2A1B, 2A2, 2B, 2C, 2D, 2E, 2F, 2G, 2H, 2I1, 2I2, 2J</t>
-        </is>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1046,11 +956,6 @@
           <t>145</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>1A1A, 1A1B, 1A2A, 1A2B, 1B1, 1B2, 2A1, 2A2, 2B1, 2B2, 2C1, 2C2, 2D1, 2D2A, 2D2B, 2D2C</t>
-        </is>
-      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1058,11 +963,6 @@
           <t>146</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>1, 2</t>
-        </is>
-      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1070,11 +970,6 @@
           <t>147</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>10, 11, 12A, 12B, 13, 14, 1A1, 1A2, 1A3, 1B1, 1B2, 1B3, 1B4, 1C, 2A, 2B, 3A, 3B, 4A, 4B, 5, 6A, 6B, 7, 8, 9A, 9B</t>
-        </is>
-      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1082,11 +977,6 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>1A, 1B, 1C, 2A, 2B, 2C</t>
-        </is>
-      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1094,11 +984,6 @@
           <t>16</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>1A, 1B, 1C, 1D, 1E, 2A, 2B</t>
-        </is>
-      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1106,11 +991,6 @@
           <t>17</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>1A, 1B, 1C, 2</t>
-        </is>
-      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1118,11 +998,6 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>1A, 1B, 1C, 1D, 1E, 1F, 1G, 1H, 1I, 1J, 2, 3A1, 3A2, 3A3, 3B1, 3B2, 3C</t>
-        </is>
-      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1130,11 +1005,6 @@
           <t>19</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 2, 20, 21, 22, 23, 24, 25, 26, 27, 28, 29, 3, 30, 31, 32, 33, 34, 35, 36, 37, 38, 39, 4, 40, 41, 42, 43, 44, 45, 46, 47, 48, 49, 5, 50, 51, 52, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1142,11 +1012,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1154,11 +1019,6 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>1, 2A, 2B1A, 2B1B, 2B2, 2B3, 2B4</t>
-        </is>
-      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1166,11 +1026,6 @@
           <t>21</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>1A, 1B1, 1B2, 2A, 2B</t>
-        </is>
-      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1178,11 +1033,6 @@
           <t>22</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1190,11 +1040,6 @@
           <t>23</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>1A, 1B, 1C, 1D1, 1D2, 1E, 1F, 1G, 1H, 2A, 2B1, 2B2, 2B3A, 2B3B, 2B4, 2C1, 2C2, 2D1, 2D2, 2D3, 2D4</t>
-        </is>
-      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1202,11 +1047,6 @@
           <t>24</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>1A, 1B, 2A, 2B1, 2B2, 2B3, 2C, 2D, 2E, 2F, 2G</t>
-        </is>
-      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1214,11 +1054,6 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>1, 2</t>
-        </is>
-      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1226,11 +1061,6 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>1, 2</t>
-        </is>
-      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1238,11 +1068,6 @@
           <t>27</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -1250,11 +1075,6 @@
           <t>28</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1262,11 +1082,6 @@
           <t>29</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>1, 2A, 2B</t>
-        </is>
-      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -1274,11 +1089,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -1286,11 +1096,6 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -1298,11 +1103,6 @@
           <t>307</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -1310,11 +1110,6 @@
           <t>31</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>1, 2</t>
-        </is>
-      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -1322,11 +1117,6 @@
           <t>32</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -1334,11 +1124,6 @@
           <t>33</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>1, 2</t>
-        </is>
-      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -1346,11 +1131,6 @@
           <t>331</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -1358,11 +1138,6 @@
           <t>34</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>1A1, 1A2, 1B, 1C1, 1C2, 1C3, 1C4, 2A, 2B, 3A1A, 3A1B, 3A2, 3B, 3C, 3D, 3E, 3F, 3G, 3H, 3I</t>
-        </is>
-      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -1370,11 +1145,6 @@
           <t>35</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4, 5, 6</t>
-        </is>
-      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -1382,11 +1152,6 @@
           <t>36</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>1A, 1B, 1C, 1D, 2</t>
-        </is>
-      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -1394,11 +1159,6 @@
           <t>37</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>1A, 1B, 1C, 2, 3A, 4B</t>
-        </is>
-      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -1406,11 +1166,6 @@
           <t>38</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>1A, 1B, 1C, 2, 3A, 3B, 3C, 3D, 3E, 3F</t>
-        </is>
-      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -1418,11 +1173,6 @@
           <t>39</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 2, 3, 4, 5A, 5B, 5C, 5D, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -1430,11 +1180,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>1A, 1B, 1C, 1D, 1E, 1F, 1G, 1H, 1I, 1J, 2</t>
-        </is>
-      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -1442,11 +1187,6 @@
           <t>40</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -1454,11 +1194,6 @@
           <t>41</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>1, 2A, 2B</t>
-        </is>
-      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -1466,11 +1201,6 @@
           <t>42</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>1A1, 1A2, 1B, 2</t>
-        </is>
-      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -1478,11 +1208,6 @@
           <t>43</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -1490,11 +1215,6 @@
           <t>44</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4, 5, 6, 7</t>
-        </is>
-      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -1502,11 +1222,6 @@
           <t>45</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4, 5, 6, 7</t>
-        </is>
-      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -1514,11 +1229,6 @@
           <t>46</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -1526,11 +1236,6 @@
           <t>47</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -1538,11 +1243,6 @@
           <t>48</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -1550,11 +1250,6 @@
           <t>49</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -1562,11 +1257,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -1574,11 +1264,6 @@
           <t>50</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>1, 2</t>
-        </is>
-      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -1586,11 +1271,6 @@
           <t>51</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>1, 2</t>
-        </is>
-      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -1598,11 +1278,6 @@
           <t>52</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -1610,11 +1285,6 @@
           <t>53</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -1622,11 +1292,6 @@
           <t>54</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>1, 2</t>
-        </is>
-      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -1634,11 +1299,6 @@
           <t>55</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>1, 2, 3</t>
-        </is>
-      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -1646,11 +1306,6 @@
           <t>56</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>1, 2</t>
-        </is>
-      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -1658,11 +1313,6 @@
           <t>57</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>1, 2, 3</t>
-        </is>
-      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -1670,11 +1320,6 @@
           <t>58</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -1682,11 +1327,6 @@
           <t>59</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>1, 2, 3</t>
-        </is>
-      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -1694,11 +1334,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>1, 2</t>
-        </is>
-      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -1706,11 +1341,6 @@
           <t>60</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>1, 2, 3</t>
-        </is>
-      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -1718,11 +1348,6 @@
           <t>61</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -1730,11 +1355,6 @@
           <t>62</t>
         </is>
       </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -1742,11 +1362,6 @@
           <t>63</t>
         </is>
       </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>1, 2, 3</t>
-        </is>
-      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -1754,11 +1369,6 @@
           <t>64</t>
         </is>
       </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>1A, 1B, 2</t>
-        </is>
-      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -1766,11 +1376,6 @@
           <t>65</t>
         </is>
       </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>1, 10, 2, 3, 4A, 4B, 5, 6, 7A1, 7A2, 7A3, 7A4, 7A5, 7A6, 7B, 7C, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -1778,11 +1383,6 @@
           <t>66</t>
         </is>
       </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4, 5, 6, 7A, 7B</t>
-        </is>
-      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -1790,11 +1390,6 @@
           <t>67</t>
         </is>
       </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>1A, 1B, 1C1, 1C2, 2A, 2B, 2C, 3, 4</t>
-        </is>
-      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -1802,11 +1397,6 @@
           <t>68</t>
         </is>
       </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -1814,11 +1404,6 @@
           <t>69</t>
         </is>
       </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>1, 10, 2, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -1826,11 +1411,6 @@
           <t>7</t>
         </is>
       </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>1, 2</t>
-        </is>
-      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -1838,11 +1418,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>1A, 1B, 2, 3, 4, 5</t>
-        </is>
-      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -1850,11 +1425,6 @@
           <t>71</t>
         </is>
       </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -1862,11 +1432,6 @@
           <t>72</t>
         </is>
       </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>1, 2</t>
-        </is>
-      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -1874,11 +1439,6 @@
           <t>73</t>
         </is>
       </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>1A, 1B, 1C, 1D, 1E, 1F, 1G, 2, 3A, 3B, 4A, 4B, 4C, 5, 6, 7, 8A, 8B, 9</t>
-        </is>
-      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -1886,11 +1446,6 @@
           <t>74</t>
         </is>
       </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4A, 4B, 4C, 4D, 5A, 5B, 5C, 5D, 6, 7</t>
-        </is>
-      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -1898,11 +1453,6 @@
           <t>75</t>
         </is>
       </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -1910,11 +1460,6 @@
           <t>76</t>
         </is>
       </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4, 5, 6, 7</t>
-        </is>
-      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -1922,11 +1467,6 @@
           <t>77</t>
         </is>
       </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>1A, 1B, 2</t>
-        </is>
-      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -1934,11 +1474,6 @@
           <t>78</t>
         </is>
       </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>1A, 1B, 2</t>
-        </is>
-      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -1946,11 +1481,6 @@
           <t>79</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -1958,11 +1488,6 @@
           <t>8</t>
         </is>
       </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>1, 8A, 8B</t>
-        </is>
-      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -1970,11 +1495,6 @@
           <t>80</t>
         </is>
       </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -1982,11 +1502,6 @@
           <t>81</t>
         </is>
       </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -1994,11 +1509,6 @@
           <t>82</t>
         </is>
       </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -2006,11 +1516,6 @@
           <t>83</t>
         </is>
       </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -2018,11 +1523,6 @@
           <t>84</t>
         </is>
       </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -2030,11 +1530,6 @@
           <t>85</t>
         </is>
       </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -2042,11 +1537,6 @@
           <t>86</t>
         </is>
       </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -2054,11 +1544,6 @@
           <t>87</t>
         </is>
       </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -2066,11 +1551,6 @@
           <t>88</t>
         </is>
       </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4</t>
-        </is>
-      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -2078,11 +1558,6 @@
           <t>89</t>
         </is>
       </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -2090,11 +1565,6 @@
           <t>9</t>
         </is>
       </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -2102,11 +1572,6 @@
           <t>90</t>
         </is>
       </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -2114,11 +1579,6 @@
           <t>91</t>
         </is>
       </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -2126,11 +1586,6 @@
           <t>92</t>
         </is>
       </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4, 5</t>
-        </is>
-      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -2138,11 +1593,6 @@
           <t>93</t>
         </is>
       </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -2150,11 +1600,6 @@
           <t>94</t>
         </is>
       </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -2162,11 +1607,6 @@
           <t>95</t>
         </is>
       </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4</t>
-        </is>
-      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -2174,11 +1614,6 @@
           <t>96</t>
         </is>
       </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>1A1, 1A2, 1B, 2</t>
-        </is>
-      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -2186,11 +1621,6 @@
           <t>97</t>
         </is>
       </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>1A1, 1B, 1C, 1D, 1E, 1F, 1G, 2, 3</t>
-        </is>
-      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -2198,21 +1628,11 @@
           <t>98</t>
         </is>
       </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>1A1, 1A2, 1B, 1C, 2, 3</t>
-        </is>
-      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
           <t>99</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>1A1A1A, 1A1A2, 1A1A3, 1A1B, 1A2, 1B, 2, 3, 4</t>
         </is>
       </c>
     </row>

--- a/out/Village_map_of_Tiruvallur_Gummidipoondi_Vanrasikuppam_13.402641_79.951224.xlsx
+++ b/out/Village_map_of_Tiruvallur_Gummidipoondi_Vanrasikuppam_13.402641_79.951224.xlsx
@@ -830,6 +830,11 @@
           <t>129</t>
         </is>
       </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 1D, 2A1, 2A2, 2B, 2C, 2D1, 2D2, 3A, 3B, 3C</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -837,6 +842,11 @@
           <t>13</t>
         </is>
       </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -844,6 +854,11 @@
           <t>130</t>
         </is>
       </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -851,6 +866,11 @@
           <t>131</t>
         </is>
       </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -858,6 +878,11 @@
           <t>132</t>
         </is>
       </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -865,6 +890,11 @@
           <t>133</t>
         </is>
       </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 1A, 1B, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -872,6 +902,11 @@
           <t>134</t>
         </is>
       </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>1, 10, 11A, 11B, 12A, 12B, 13, 14, 15, 16, 17, 18A, 18B, 19, 20, 21, 2A, 2B, 3A, 3B, 4A, 4B, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -879,6 +914,11 @@
           <t>135</t>
         </is>
       </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -886,6 +926,11 @@
           <t>136</t>
         </is>
       </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>10, 11, 1A, 1B, 2, 3, 4, 5A, 5B, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -893,6 +938,11 @@
           <t>137</t>
         </is>
       </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 2, 3, 4, 5, 6, 7, 8, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -900,6 +950,11 @@
           <t>138</t>
         </is>
       </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -907,6 +962,11 @@
           <t>139</t>
         </is>
       </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -914,6 +974,11 @@
           <t>14</t>
         </is>
       </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 2C, 3A, 3B, 3C, 3D, 4A, 4B, 4C, 4D, 4E, 4F</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -921,6 +986,11 @@
           <t>140</t>
         </is>
       </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -928,6 +998,11 @@
           <t>141</t>
         </is>
       </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -935,6 +1010,11 @@
           <t>142</t>
         </is>
       </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -942,6 +1022,11 @@
           <t>143</t>
         </is>
       </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13A, 13B, 2, 3, 4, 5, 6, 7, 8, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -949,6 +1034,11 @@
           <t>144</t>
         </is>
       </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 1D, 2A1A, 2A1B, 2A2, 2B, 2C, 2D, 2E, 2F, 2G, 2H, 2I1, 2I2, 2J</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -956,6 +1046,11 @@
           <t>145</t>
         </is>
       </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>1A1A, 1A1B, 1A2A, 1A2B, 1B1, 1B2, 2A1, 2A2, 2B1, 2B2, 2C1, 2C2, 2D1, 2D2A, 2D2B, 2D2C</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -963,6 +1058,11 @@
           <t>146</t>
         </is>
       </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -970,6 +1070,11 @@
           <t>147</t>
         </is>
       </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>10, 11, 12A, 12B, 13, 14, 1A1, 1A2, 1A3, 1B1, 1B2, 1B3, 1B4, 1C, 2A, 2B, 3A, 3B, 4A, 4B, 5, 6A, 6B, 7, 8, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -977,6 +1082,11 @@
           <t>15</t>
         </is>
       </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 2A, 2B, 2C</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -984,6 +1094,11 @@
           <t>16</t>
         </is>
       </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 1D, 1E, 2A, 2B</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -991,6 +1106,11 @@
           <t>17</t>
         </is>
       </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 2</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -998,6 +1118,11 @@
           <t>18</t>
         </is>
       </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 1D, 1E, 1F, 1G, 1H, 1I, 1J, 2, 3A1, 3A2, 3A3, 3B1, 3B2, 3C</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1005,6 +1130,11 @@
           <t>19</t>
         </is>
       </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 2, 20, 21, 22, 23, 24, 25, 26, 27, 28, 29, 3, 30, 31, 32, 33, 34, 35, 36, 37, 38, 39, 4, 40, 41, 42, 43, 44, 45, 46, 47, 48, 49, 5, 50, 51, 52, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1012,6 +1142,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1019,6 +1154,11 @@
           <t>20</t>
         </is>
       </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B1A, 2B1B, 2B2, 2B3, 2B4</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1026,6 +1166,11 @@
           <t>21</t>
         </is>
       </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>1A, 1B1, 1B2, 2A, 2B</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1033,6 +1178,11 @@
           <t>22</t>
         </is>
       </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1040,6 +1190,11 @@
           <t>23</t>
         </is>
       </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 1D1, 1D2, 1E, 1F, 1G, 1H, 2A, 2B1, 2B2, 2B3A, 2B3B, 2B4, 2C1, 2C2, 2D1, 2D2, 2D3, 2D4</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1047,6 +1202,11 @@
           <t>24</t>
         </is>
       </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2A, 2B1, 2B2, 2B3, 2C, 2D, 2E, 2F, 2G</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1054,6 +1214,11 @@
           <t>25</t>
         </is>
       </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1061,6 +1226,11 @@
           <t>26</t>
         </is>
       </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1068,6 +1238,11 @@
           <t>27</t>
         </is>
       </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -1075,6 +1250,11 @@
           <t>28</t>
         </is>
       </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1082,6 +1262,11 @@
           <t>29</t>
         </is>
       </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -1089,6 +1274,11 @@
           <t>3</t>
         </is>
       </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -1096,6 +1286,11 @@
           <t>30</t>
         </is>
       </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -1103,6 +1298,11 @@
           <t>307</t>
         </is>
       </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -1110,6 +1310,11 @@
           <t>31</t>
         </is>
       </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -1117,6 +1322,11 @@
           <t>32</t>
         </is>
       </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -1124,6 +1334,11 @@
           <t>33</t>
         </is>
       </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -1131,6 +1346,11 @@
           <t>331</t>
         </is>
       </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -1138,6 +1358,11 @@
           <t>34</t>
         </is>
       </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1B, 1C1, 1C2, 1C3, 1C4, 2A, 2B, 3A1A, 3A1B, 3A2, 3B, 3C, 3D, 3E, 3F, 3G, 3H, 3I</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -1145,6 +1370,11 @@
           <t>35</t>
         </is>
       </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -1152,6 +1382,11 @@
           <t>36</t>
         </is>
       </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 1D, 2</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -1159,6 +1394,11 @@
           <t>37</t>
         </is>
       </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 2, 3A, 4B</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -1166,6 +1406,11 @@
           <t>38</t>
         </is>
       </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 2, 3A, 3B, 3C, 3D, 3E, 3F</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -1173,6 +1418,11 @@
           <t>39</t>
         </is>
       </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 2, 3, 4, 5A, 5B, 5C, 5D, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -1180,6 +1430,11 @@
           <t>4</t>
         </is>
       </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 1D, 1E, 1F, 1G, 1H, 1I, 1J, 2</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -1187,6 +1442,11 @@
           <t>40</t>
         </is>
       </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -1194,6 +1454,11 @@
           <t>41</t>
         </is>
       </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -1201,6 +1466,11 @@
           <t>42</t>
         </is>
       </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1B, 2</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -1208,6 +1478,11 @@
           <t>43</t>
         </is>
       </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -1215,6 +1490,11 @@
           <t>44</t>
         </is>
       </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6, 7</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -1222,6 +1502,11 @@
           <t>45</t>
         </is>
       </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6, 7</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -1229,6 +1514,11 @@
           <t>46</t>
         </is>
       </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -1236,6 +1526,11 @@
           <t>47</t>
         </is>
       </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -1243,6 +1538,11 @@
           <t>48</t>
         </is>
       </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -1250,6 +1550,11 @@
           <t>49</t>
         </is>
       </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -1257,6 +1562,11 @@
           <t>5</t>
         </is>
       </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -1264,6 +1574,11 @@
           <t>50</t>
         </is>
       </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -1271,6 +1586,11 @@
           <t>51</t>
         </is>
       </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -1278,6 +1598,11 @@
           <t>52</t>
         </is>
       </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -1285,6 +1610,11 @@
           <t>53</t>
         </is>
       </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -1292,6 +1622,11 @@
           <t>54</t>
         </is>
       </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -1299,6 +1634,11 @@
           <t>55</t>
         </is>
       </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -1306,6 +1646,11 @@
           <t>56</t>
         </is>
       </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -1313,6 +1658,11 @@
           <t>57</t>
         </is>
       </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -1320,6 +1670,11 @@
           <t>58</t>
         </is>
       </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -1327,6 +1682,11 @@
           <t>59</t>
         </is>
       </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -1334,6 +1694,11 @@
           <t>6</t>
         </is>
       </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -1341,6 +1706,11 @@
           <t>60</t>
         </is>
       </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -1348,6 +1718,11 @@
           <t>61</t>
         </is>
       </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -1355,11 +1730,21 @@
           <t>62</t>
         </is>
       </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
           <t>63</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
         </is>
       </c>
     </row>

--- a/out/Village_map_of_Tiruvallur_Gummidipoondi_Vanrasikuppam_13.402641_79.951224.xlsx
+++ b/out/Village_map_of_Tiruvallur_Gummidipoondi_Vanrasikuppam_13.402641_79.951224.xlsx
@@ -1754,6 +1754,11 @@
           <t>64</t>
         </is>
       </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -1761,6 +1766,11 @@
           <t>65</t>
         </is>
       </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>1, 10, 2, 3, 4A, 4B, 5, 6, 7A1, 7A2, 7A3, 7A4, 7A5, 7A6, 7B, 7C, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -1768,6 +1778,11 @@
           <t>66</t>
         </is>
       </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6, 7A, 7B</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -1775,6 +1790,11 @@
           <t>67</t>
         </is>
       </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C1, 1C2, 2A, 2B, 2C, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -1782,6 +1802,11 @@
           <t>68</t>
         </is>
       </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -1789,6 +1814,11 @@
           <t>69</t>
         </is>
       </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>1, 10, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -1796,6 +1826,11 @@
           <t>7</t>
         </is>
       </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -1803,6 +1838,11 @@
           <t>70</t>
         </is>
       </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2, 3, 4, 5</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -1810,6 +1850,11 @@
           <t>71</t>
         </is>
       </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -1817,6 +1862,11 @@
           <t>72</t>
         </is>
       </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -1824,6 +1874,11 @@
           <t>73</t>
         </is>
       </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 1D, 1E, 1F, 1G, 2, 3A, 3B, 4A, 4B, 4C, 5, 6, 7, 8A, 8B, 9</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -1831,6 +1886,11 @@
           <t>74</t>
         </is>
       </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4A, 4B, 4C, 4D, 5A, 5B, 5C, 5D, 6, 7</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -1838,6 +1898,11 @@
           <t>75</t>
         </is>
       </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -1845,6 +1910,11 @@
           <t>76</t>
         </is>
       </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6, 7</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -1852,6 +1922,11 @@
           <t>77</t>
         </is>
       </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -1859,6 +1934,11 @@
           <t>78</t>
         </is>
       </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -1866,6 +1946,11 @@
           <t>79</t>
         </is>
       </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -1873,6 +1958,11 @@
           <t>8</t>
         </is>
       </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>1, 8A, 8B</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -1880,6 +1970,11 @@
           <t>80</t>
         </is>
       </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -1887,6 +1982,11 @@
           <t>81</t>
         </is>
       </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -1894,6 +1994,11 @@
           <t>82</t>
         </is>
       </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -1901,6 +2006,11 @@
           <t>83</t>
         </is>
       </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -1908,6 +2018,11 @@
           <t>84</t>
         </is>
       </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -1915,6 +2030,11 @@
           <t>85</t>
         </is>
       </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -1922,6 +2042,11 @@
           <t>86</t>
         </is>
       </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -1929,6 +2054,11 @@
           <t>87</t>
         </is>
       </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -1936,6 +2066,11 @@
           <t>88</t>
         </is>
       </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -1943,6 +2078,11 @@
           <t>89</t>
         </is>
       </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -1950,6 +2090,11 @@
           <t>9</t>
         </is>
       </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -1957,6 +2102,11 @@
           <t>90</t>
         </is>
       </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -1964,6 +2114,11 @@
           <t>91</t>
         </is>
       </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -1971,6 +2126,11 @@
           <t>92</t>
         </is>
       </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -1978,6 +2138,11 @@
           <t>93</t>
         </is>
       </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -1985,6 +2150,11 @@
           <t>94</t>
         </is>
       </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -1992,6 +2162,11 @@
           <t>95</t>
         </is>
       </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -1999,6 +2174,11 @@
           <t>96</t>
         </is>
       </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1B, 2</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -2006,6 +2186,11 @@
           <t>97</t>
         </is>
       </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>1A1, 1B, 1C, 1D, 1E, 1F, 1G, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -2013,11 +2198,21 @@
           <t>98</t>
         </is>
       </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1B, 1C, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
           <t>99</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>1A1A1A, 1A1A2, 1A1A3, 1A1B, 1A2, 1B, 2, 3, 4</t>
         </is>
       </c>
     </row>

--- a/out/Village_map_of_Tiruvallur_Gummidipoondi_Vanrasikuppam_13.402641_79.951224.xlsx
+++ b/out/Village_map_of_Tiruvallur_Gummidipoondi_Vanrasikuppam_13.402641_79.951224.xlsx
@@ -950,6 +950,11 @@
           <t>138</t>
         </is>
       </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -957,6 +962,11 @@
           <t>139</t>
         </is>
       </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -964,6 +974,11 @@
           <t>14</t>
         </is>
       </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 2C, 3A, 3B, 3C, 3D, 4A, 4B, 4C, 4D, 4E, 4F</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -971,6 +986,11 @@
           <t>140</t>
         </is>
       </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -978,6 +998,11 @@
           <t>141</t>
         </is>
       </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -985,6 +1010,11 @@
           <t>142</t>
         </is>
       </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -992,6 +1022,11 @@
           <t>143</t>
         </is>
       </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13A, 13B, 2, 3, 4, 5, 6, 7, 8, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -999,6 +1034,11 @@
           <t>144</t>
         </is>
       </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 1D, 2A1A, 2A1B, 2A2, 2B, 2C, 2D, 2E, 2F, 2G, 2H, 2I1, 2I2, 2J</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1006,6 +1046,11 @@
           <t>145</t>
         </is>
       </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>1A1A, 1A1B, 1A2A, 1A2B, 1B1, 1B2, 2A1, 2A2, 2B1, 2B2, 2C1, 2C2, 2D1, 2D2A, 2D2B, 2D2C</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1013,6 +1058,11 @@
           <t>146</t>
         </is>
       </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1020,6 +1070,11 @@
           <t>147</t>
         </is>
       </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>10, 11, 12A, 12B, 13, 14, 1A1, 1A2, 1A3, 1B1, 1B2, 1B3, 1B4, 1C, 2A, 2B, 3A, 3B, 4A, 4B, 5, 6A, 6B, 7, 8, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1027,6 +1082,11 @@
           <t>15</t>
         </is>
       </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 2A, 2B, 2C</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1034,6 +1094,11 @@
           <t>16</t>
         </is>
       </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 1D, 1E, 2A, 2B</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1041,6 +1106,11 @@
           <t>17</t>
         </is>
       </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 2</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1048,6 +1118,11 @@
           <t>18</t>
         </is>
       </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 1D, 1E, 1F, 1G, 1H, 1I, 1J, 2, 3A1, 3A2, 3A3, 3B1, 3B2, 3C</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1055,6 +1130,11 @@
           <t>19</t>
         </is>
       </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 2, 20, 21, 22, 23, 24, 25, 26, 27, 28, 29, 3, 30, 31, 32, 33, 34, 35, 36, 37, 38, 39, 4, 40, 41, 42, 43, 44, 45, 46, 47, 48, 49, 5, 50, 51, 52, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1062,6 +1142,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1069,6 +1154,11 @@
           <t>20</t>
         </is>
       </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B1A, 2B1B, 2B2, 2B3, 2B4</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1076,6 +1166,11 @@
           <t>21</t>
         </is>
       </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>1A, 1B1, 1B2, 2A, 2B</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1083,6 +1178,11 @@
           <t>22</t>
         </is>
       </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1090,6 +1190,11 @@
           <t>23</t>
         </is>
       </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 1D1, 1D2, 1E, 1F, 1G, 1H, 2A, 2B1, 2B2, 2B3A, 2B3B, 2B4, 2C1, 2C2, 2D1, 2D2, 2D3, 2D4</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1097,6 +1202,11 @@
           <t>24</t>
         </is>
       </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2A, 2B1, 2B2, 2B3, 2C, 2D, 2E, 2F, 2G</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1104,6 +1214,11 @@
           <t>25</t>
         </is>
       </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1111,6 +1226,11 @@
           <t>26</t>
         </is>
       </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1118,6 +1238,11 @@
           <t>27</t>
         </is>
       </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -1125,6 +1250,11 @@
           <t>28</t>
         </is>
       </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1132,6 +1262,11 @@
           <t>29</t>
         </is>
       </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -1139,6 +1274,11 @@
           <t>3</t>
         </is>
       </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -1146,6 +1286,11 @@
           <t>30</t>
         </is>
       </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -1153,6 +1298,11 @@
           <t>307</t>
         </is>
       </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -1160,6 +1310,11 @@
           <t>31</t>
         </is>
       </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -1167,6 +1322,11 @@
           <t>32</t>
         </is>
       </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -1174,6 +1334,11 @@
           <t>33</t>
         </is>
       </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -1181,6 +1346,11 @@
           <t>331</t>
         </is>
       </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -1188,6 +1358,11 @@
           <t>34</t>
         </is>
       </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1B, 1C1, 1C2, 1C3, 1C4, 2A, 2B, 3A1A, 3A1B, 3A2, 3B, 3C, 3D, 3E, 3F, 3G, 3H, 3I</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -1195,6 +1370,11 @@
           <t>35</t>
         </is>
       </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -1202,6 +1382,11 @@
           <t>36</t>
         </is>
       </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 1D, 2</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -1209,6 +1394,11 @@
           <t>37</t>
         </is>
       </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 2, 3A, 4B</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -1216,6 +1406,11 @@
           <t>38</t>
         </is>
       </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 2, 3A, 3B, 3C, 3D, 3E, 3F</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -1223,6 +1418,11 @@
           <t>39</t>
         </is>
       </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 2, 3, 4, 5A, 5B, 5C, 5D, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -1230,6 +1430,11 @@
           <t>4</t>
         </is>
       </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 1D, 1E, 1F, 1G, 1H, 1I, 1J, 2</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -1237,6 +1442,11 @@
           <t>40</t>
         </is>
       </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -1244,6 +1454,11 @@
           <t>41</t>
         </is>
       </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -1251,6 +1466,11 @@
           <t>42</t>
         </is>
       </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1B, 2</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -1258,6 +1478,11 @@
           <t>43</t>
         </is>
       </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -1265,6 +1490,11 @@
           <t>44</t>
         </is>
       </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6, 7</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -1272,6 +1502,11 @@
           <t>45</t>
         </is>
       </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6, 7</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -1279,6 +1514,11 @@
           <t>46</t>
         </is>
       </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -1286,6 +1526,11 @@
           <t>47</t>
         </is>
       </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -1293,6 +1538,11 @@
           <t>48</t>
         </is>
       </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -1300,6 +1550,11 @@
           <t>49</t>
         </is>
       </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -1307,6 +1562,11 @@
           <t>5</t>
         </is>
       </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -1314,6 +1574,11 @@
           <t>50</t>
         </is>
       </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -1321,6 +1586,11 @@
           <t>51</t>
         </is>
       </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -1328,6 +1598,11 @@
           <t>52</t>
         </is>
       </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -1335,6 +1610,11 @@
           <t>53</t>
         </is>
       </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -1342,6 +1622,11 @@
           <t>54</t>
         </is>
       </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -1349,6 +1634,11 @@
           <t>55</t>
         </is>
       </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -1356,6 +1646,11 @@
           <t>56</t>
         </is>
       </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -1363,6 +1658,11 @@
           <t>57</t>
         </is>
       </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -1370,6 +1670,11 @@
           <t>58</t>
         </is>
       </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -1377,6 +1682,11 @@
           <t>59</t>
         </is>
       </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -1384,6 +1694,11 @@
           <t>6</t>
         </is>
       </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -1391,6 +1706,11 @@
           <t>60</t>
         </is>
       </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -1398,6 +1718,11 @@
           <t>61</t>
         </is>
       </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -1405,6 +1730,11 @@
           <t>62</t>
         </is>
       </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -1412,6 +1742,11 @@
           <t>63</t>
         </is>
       </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -1419,6 +1754,11 @@
           <t>64</t>
         </is>
       </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -1426,6 +1766,11 @@
           <t>65</t>
         </is>
       </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>1, 10, 2, 3, 4A, 4B, 5, 6, 7A1, 7A2, 7A3, 7A4, 7A5, 7A6, 7B, 7C, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -1433,6 +1778,11 @@
           <t>66</t>
         </is>
       </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6, 7A, 7B</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -1440,6 +1790,11 @@
           <t>67</t>
         </is>
       </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C1, 1C2, 2A, 2B, 2C, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -1447,6 +1802,11 @@
           <t>68</t>
         </is>
       </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -1454,6 +1814,11 @@
           <t>69</t>
         </is>
       </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>1, 10, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -1461,6 +1826,11 @@
           <t>7</t>
         </is>
       </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -1468,6 +1838,11 @@
           <t>70</t>
         </is>
       </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2, 3, 4, 5</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -1475,6 +1850,11 @@
           <t>71</t>
         </is>
       </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -1482,6 +1862,11 @@
           <t>72</t>
         </is>
       </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -1489,6 +1874,11 @@
           <t>73</t>
         </is>
       </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 1D, 1E, 1F, 1G, 2, 3A, 3B, 4A, 4B, 4C, 5, 6, 7, 8A, 8B, 9</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -1496,6 +1886,11 @@
           <t>74</t>
         </is>
       </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4A, 4B, 4C, 4D, 5A, 5B, 5C, 5D, 6, 7</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -1503,6 +1898,11 @@
           <t>75</t>
         </is>
       </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -1510,6 +1910,11 @@
           <t>76</t>
         </is>
       </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6, 7</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -1517,6 +1922,11 @@
           <t>77</t>
         </is>
       </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -1524,6 +1934,11 @@
           <t>78</t>
         </is>
       </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -1531,6 +1946,11 @@
           <t>79</t>
         </is>
       </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -1538,6 +1958,11 @@
           <t>8</t>
         </is>
       </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>1, 8A, 8B</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -1545,6 +1970,11 @@
           <t>80</t>
         </is>
       </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -1552,6 +1982,11 @@
           <t>81</t>
         </is>
       </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -1559,6 +1994,11 @@
           <t>82</t>
         </is>
       </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -1566,6 +2006,11 @@
           <t>83</t>
         </is>
       </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -1573,6 +2018,11 @@
           <t>84</t>
         </is>
       </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -1580,6 +2030,11 @@
           <t>85</t>
         </is>
       </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -1587,6 +2042,11 @@
           <t>86</t>
         </is>
       </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -1594,6 +2054,11 @@
           <t>87</t>
         </is>
       </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -1601,6 +2066,11 @@
           <t>88</t>
         </is>
       </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -1608,6 +2078,11 @@
           <t>89</t>
         </is>
       </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -1615,6 +2090,11 @@
           <t>9</t>
         </is>
       </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -1622,6 +2102,11 @@
           <t>90</t>
         </is>
       </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -1629,6 +2114,11 @@
           <t>91</t>
         </is>
       </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -1636,6 +2126,11 @@
           <t>92</t>
         </is>
       </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -1643,6 +2138,11 @@
           <t>93</t>
         </is>
       </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -1650,6 +2150,11 @@
           <t>94</t>
         </is>
       </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -1657,11 +2162,21 @@
           <t>95</t>
         </is>
       </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
           <t>96</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1B, 2</t>
         </is>
       </c>
     </row>

--- a/out/Village_map_of_Tiruvallur_Gummidipoondi_Vanrasikuppam_13.402641_79.951224.xlsx
+++ b/out/Village_map_of_Tiruvallur_Gummidipoondi_Vanrasikuppam_13.402641_79.951224.xlsx
@@ -2186,6 +2186,11 @@
           <t>97</t>
         </is>
       </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>1A1, 1B, 1C, 1D, 1E, 1F, 1G, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -2193,11 +2198,21 @@
           <t>98</t>
         </is>
       </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1B, 1C, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
           <t>99</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>1A1A1A, 1A1A2, 1A1A3, 1A1B, 1A2, 1B, 2, 3, 4</t>
         </is>
       </c>
     </row>
